--- a/projects/karrot-fresh/당근마켓_마진계산기.xlsx
+++ b/projects/karrot-fresh/당근마켓_마진계산기.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="설정" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="성주참외" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="미니밤호박(보우짱)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="홍감자" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="콜라비" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="대극천복숭아" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="미니밤호박(보우짱)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="홍감자" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="콜라비" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1650,6 +1651,345 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🥕 대극천복숭아 — 당근 마진계산 (수수료 3.3% 반영)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>🟩공급가 실측(영천·김천 등 국내산,롯데택배,일반박스+쉘 벌크포장 포함,5~7월중순). 시세=쿠팡(로얄대과 1kg18,800·2kg28,800). 소과=11~16과/kg, 로얄과=4~10과/kg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>옵션</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>실중량</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>공급가(택배·포장포함)</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>건당광고비</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>당근수수료(3.3%)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>총비용</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>시중시세(쿠팡)</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>손익분기가</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>당근권장가</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>마진(원)</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>마진율</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>로얄과</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>4~10과</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>9300</v>
+      </c>
+      <c r="E4" s="6">
+        <f>'설정'!$B$5</f>
+        <v/>
+      </c>
+      <c r="F4" s="6">
+        <f>J4*'설정'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
+        <f>D4+E4+F4</f>
+        <v/>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>18800</v>
+      </c>
+      <c r="I4" s="6">
+        <f>ROUND((D4+E4)/(1-'설정'!$B$6),-2)</f>
+        <v/>
+      </c>
+      <c r="J4" s="15">
+        <f>ROUND(MAX(H4,(D4+E4)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
+        <v/>
+      </c>
+      <c r="K4" s="16">
+        <f>J4-G4</f>
+        <v/>
+      </c>
+      <c r="L4" s="17">
+        <f>IF(J4=0,0,K4/J4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="8">
+        <f>IF(H4&lt;I4,"⚠️시세&lt;손익분기:손해",IF(J4&gt;H4,"권장가&gt;시세(마진확보↑)","✅시세매칭 OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>로얄과</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>8~20과</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E5" s="6">
+        <f>'설정'!$B$5</f>
+        <v/>
+      </c>
+      <c r="F5" s="6">
+        <f>J5*'설정'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G5" s="13">
+        <f>D5+E5+F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>28800</v>
+      </c>
+      <c r="I5" s="6">
+        <f>ROUND((D5+E5)/(1-'설정'!$B$6),-2)</f>
+        <v/>
+      </c>
+      <c r="J5" s="15">
+        <f>ROUND(MAX(H5,(D5+E5)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
+        <v/>
+      </c>
+      <c r="K5" s="16">
+        <f>J5-G5</f>
+        <v/>
+      </c>
+      <c r="L5" s="17">
+        <f>IF(J5=0,0,K5/J5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="8">
+        <f>IF(H5&lt;I5,"⚠️시세&lt;손익분기:손해",IF(J5&gt;H5,"권장가&gt;시세(마진확보↑)","✅시세매칭 OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>소과</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>11~16과</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>6900</v>
+      </c>
+      <c r="E6" s="6">
+        <f>'설정'!$B$5</f>
+        <v/>
+      </c>
+      <c r="F6" s="6">
+        <f>J6*'설정'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G6" s="13">
+        <f>D6+E6+F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>14800</v>
+      </c>
+      <c r="I6" s="6">
+        <f>ROUND((D6+E6)/(1-'설정'!$B$6),-2)</f>
+        <v/>
+      </c>
+      <c r="J6" s="15">
+        <f>ROUND(MAX(H6,(D6+E6)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
+        <v/>
+      </c>
+      <c r="K6" s="16">
+        <f>J6-G6</f>
+        <v/>
+      </c>
+      <c r="L6" s="17">
+        <f>IF(J6=0,0,K6/J6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="8">
+        <f>IF(H6&lt;I6,"⚠️시세&lt;손익분기:손해",IF(J6&gt;H6,"권장가&gt;시세(마진확보↑)","✅시세매칭 OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>소과</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>21~32과</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E7" s="6">
+        <f>'설정'!$B$5</f>
+        <v/>
+      </c>
+      <c r="F7" s="6">
+        <f>J7*'설정'!$B$6</f>
+        <v/>
+      </c>
+      <c r="G7" s="13">
+        <f>D7+E7+F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>22800</v>
+      </c>
+      <c r="I7" s="6">
+        <f>ROUND((D7+E7)/(1-'설정'!$B$6),-2)</f>
+        <v/>
+      </c>
+      <c r="J7" s="15">
+        <f>ROUND(MAX(H7,(D7+E7)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
+        <v/>
+      </c>
+      <c r="K7" s="16">
+        <f>J7-G7</f>
+        <v/>
+      </c>
+      <c r="L7" s="17">
+        <f>IF(J7=0,0,K7/J7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="8">
+        <f>IF(H7&lt;I7,"⚠️시세&lt;손익분기:손해",IF(J7&gt;H7,"권장가&gt;시세(마진확보↑)","✅시세매칭 OK"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="K4:K7">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2148,7 +2488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3287,7 +3627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/projects/karrot-fresh/당근마켓_마진계산기.xlsx
+++ b/projects/karrot-fresh/당근마켓_마진계산기.xlsx
@@ -13,6 +13,7 @@
     <sheet name="미니밤호박(보우짱)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="홍감자" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="콜라비" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="경쟁사비교(복숭아)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +48,10 @@
     </font>
     <font>
       <color rgb="00548235"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -119,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -171,6 +176,12 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3897,4 +3908,411 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🥊 경쟁사 가격 대결 — 대극천복숭아 (당근 무료배송 경쟁사 vs 우리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>대응권장가=경쟁사보다 300원↓(단 손익분기 이상). 마진/손익분기는 설정값(광고·수수료3.3%) 자동 연동. 그램당으로 보면 경쟁사 3kg가 진짜 무기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>경쟁사 옵션</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>경쟁사가</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>경쟁사 100g당</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>우리 매칭</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>우리 공급가</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>우리 손익분기</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>대응 권장가</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>우리 마진</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>우리 마진율</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>우리 100g당</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>소과 2kg(60g/개)</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="n">
+        <v>16100</v>
+      </c>
+      <c r="C4" s="16">
+        <f>ROUND(B4/20.0,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>우리 소과 2kg</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F4" s="6">
+        <f>ROUND((E4+'설정'!$B$5)/(1-'설정'!$B$6),-2)</f>
+        <v/>
+      </c>
+      <c r="G4" s="15">
+        <f>ROUND(MAX(F4,B4-300),-2)</f>
+        <v/>
+      </c>
+      <c r="H4" s="16">
+        <f>G4*(1-'설정'!$B$6)-E4-'설정'!$B$5</f>
+        <v/>
+      </c>
+      <c r="I4" s="17">
+        <f>IF(G4=0,0,H4/G4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="16">
+        <f>ROUND(G4/20.0,0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="19">
+        <f>IF(B4-300&gt;=F4,"✅ 이길 수 있음","⚠️ 빠듯")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>중과 2kg(80g/개)</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>18200</v>
+      </c>
+      <c r="C5" s="16">
+        <f>ROUND(B5/20.0,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>우리 소과 2kg</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F5" s="6">
+        <f>ROUND((E5+'설정'!$B$5)/(1-'설정'!$B$6),-2)</f>
+        <v/>
+      </c>
+      <c r="G5" s="15">
+        <f>ROUND(MAX(F5,B5-300),-2)</f>
+        <v/>
+      </c>
+      <c r="H5" s="16">
+        <f>G5*(1-'설정'!$B$6)-E5-'설정'!$B$5</f>
+        <v/>
+      </c>
+      <c r="I5" s="17">
+        <f>IF(G5=0,0,H5/G5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="16">
+        <f>ROUND(G5/20.0,0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="19">
+        <f>IF(B5-300&gt;=F5,"✅ 이길 수 있음","⚠️ 빠듯")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>대과 2kg(100g/개)</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C6" s="16">
+        <f>ROUND(B6/20.0,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>우리 로얄과 2kg</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F6" s="6">
+        <f>ROUND((E6+'설정'!$B$5)/(1-'설정'!$B$6),-2)</f>
+        <v/>
+      </c>
+      <c r="G6" s="15">
+        <f>ROUND(MAX(F6,B6-300),-2)</f>
+        <v/>
+      </c>
+      <c r="H6" s="16">
+        <f>G6*(1-'설정'!$B$6)-E6-'설정'!$B$5</f>
+        <v/>
+      </c>
+      <c r="I6" s="17">
+        <f>IF(G6=0,0,H6/G6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="16">
+        <f>ROUND(G6/20.0,0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="19">
+        <f>IF(B6-300&gt;=F6,"✅ 이길 수 있음","⚠️ 빠듯")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>소과 3kg(60g/개)</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>20800</v>
+      </c>
+      <c r="C7" s="16">
+        <f>ROUND(B7/30.0,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>우리 3kg 공급 없음</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>❓3kg 매입가 협의 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>중과 3kg(80g/개)</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>21500</v>
+      </c>
+      <c r="C8" s="16">
+        <f>ROUND(B8/30.0,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>우리 3kg 공급 없음</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
+        <is>
+          <t>❓3kg 매입가 협의 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>대과 3kg(100g/개)</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>25200</v>
+      </c>
+      <c r="C9" s="16">
+        <f>ROUND(B9/30.0,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>우리 3kg 공급 없음</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="inlineStr">
+        <is>
+          <t>❓3kg 매입가 협의 필요</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H4:H9">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/karrot-fresh/당근마켓_마진계산기.xlsx
+++ b/projects/karrot-fresh/당근마켓_마진계산기.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="설정" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="성주참외" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="대극천복숭아" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="미니밤호박(보우짱)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="홍감자" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="콜라비" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="경쟁사비교(복숭아)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="요약(전상품)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="성주참외" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="대극천복숭아" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="미니밤호박(보우짱)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="홍감자" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="콜라비" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="경쟁사비교(복숭아)" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -124,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -150,14 +151,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -171,16 +182,7 @@
     <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -730,6 +732,468 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🏆 전상품 마진 랭킹 — 광고비 배분 우선순위 (설정 변경 시 자동 갱신)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>대표옵션</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>권장판매가</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>마진(원)</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>마진율</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>전략</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>성주참외</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>로얄 5kg</t>
+        </is>
+      </c>
+      <c r="D3" s="12">
+        <f>'성주참외'!J7</f>
+        <v/>
+      </c>
+      <c r="E3" s="12">
+        <f>'성주참외'!K7</f>
+        <v/>
+      </c>
+      <c r="F3" s="13">
+        <f>'성주참외'!L7</f>
+        <v/>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>광고 집중 1순위 (마진 60%대)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>성주참외</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>가성비 5kg</t>
+        </is>
+      </c>
+      <c r="D4" s="12">
+        <f>'성주참외'!J17</f>
+        <v/>
+      </c>
+      <c r="E4" s="12">
+        <f>'성주참외'!K17</f>
+        <v/>
+      </c>
+      <c r="F4" s="13">
+        <f>'성주참외'!L17</f>
+        <v/>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>박리다매 라인 (60%대)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>성주참외</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>로얄 10kg</t>
+        </is>
+      </c>
+      <c r="D5" s="12">
+        <f>'성주참외'!J8</f>
+        <v/>
+      </c>
+      <c r="E5" s="12">
+        <f>'성주참외'!K8</f>
+        <v/>
+      </c>
+      <c r="F5" s="13">
+        <f>'성주참외'!L8</f>
+        <v/>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>객단가 최대화</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>미니밤호박(보우짱)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>로얄 10kg</t>
+        </is>
+      </c>
+      <c r="D6" s="12">
+        <f>'미니밤호박(보우짱)'!J10</f>
+        <v/>
+      </c>
+      <c r="E6" s="12">
+        <f>'미니밤호박(보우짱)'!K10</f>
+        <v/>
+      </c>
+      <c r="F6" s="13">
+        <f>'미니밤호박(보우짱)'!L10</f>
+        <v/>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>✳️정정: 손해 아님, 효자(36%+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>대극천복숭아</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>소과 2kg</t>
+        </is>
+      </c>
+      <c r="D7" s="12">
+        <f>'대극천복숭아'!J7</f>
+        <v/>
+      </c>
+      <c r="E7" s="12">
+        <f>'대극천복숭아'!K7</f>
+        <v/>
+      </c>
+      <c r="F7" s="13">
+        <f>'대극천복숭아'!L7</f>
+        <v/>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>경쟁사 언더컷 가능(경쟁사비교 시트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>대극천복숭아</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>로얄 2kg</t>
+        </is>
+      </c>
+      <c r="D8" s="12">
+        <f>'대극천복숭아'!J5</f>
+        <v/>
+      </c>
+      <c r="E8" s="12">
+        <f>'대극천복숭아'!K5</f>
+        <v/>
+      </c>
+      <c r="F8" s="13">
+        <f>'대극천복숭아'!L5</f>
+        <v/>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>등급우위(우리 로얄&gt;저쪽 대과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>미니밤호박(보우짱)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>로얄 2kg</t>
+        </is>
+      </c>
+      <c r="D9" s="12">
+        <f>'미니밤호박(보우짱)'!J5</f>
+        <v/>
+      </c>
+      <c r="E9" s="12">
+        <f>'미니밤호박(보우짱)'!K5</f>
+        <v/>
+      </c>
+      <c r="F9" s="13">
+        <f>'미니밤호박(보우짱)'!L5</f>
+        <v/>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>기본 라인</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>홍감자</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>대 5kg</t>
+        </is>
+      </c>
+      <c r="D10" s="12">
+        <f>'홍감자'!J15</f>
+        <v/>
+      </c>
+      <c r="E10" s="12">
+        <f>'홍감자'!K15</f>
+        <v/>
+      </c>
+      <c r="F10" s="13">
+        <f>'홍감자'!L15</f>
+        <v/>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>안정 라인(20%대)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>홍감자</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>특 5kg</t>
+        </is>
+      </c>
+      <c r="D11" s="12">
+        <f>'홍감자'!J19</f>
+        <v/>
+      </c>
+      <c r="E11" s="12">
+        <f>'홍감자'!K19</f>
+        <v/>
+      </c>
+      <c r="F11" s="13">
+        <f>'홍감자'!L19</f>
+        <v/>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>프리미엄 라인</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>콜라비</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>정품 5kg</t>
+        </is>
+      </c>
+      <c r="D12" s="12">
+        <f>'콜라비'!J5</f>
+        <v/>
+      </c>
+      <c r="E12" s="12">
+        <f>'콜라비'!K5</f>
+        <v/>
+      </c>
+      <c r="F12" s="13">
+        <f>'콜라비'!L5</f>
+        <v/>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>저마진, 구색용</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>콜라비</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>정품 3kg</t>
+        </is>
+      </c>
+      <c r="D13" s="12">
+        <f>'콜라비'!J4</f>
+        <v/>
+      </c>
+      <c r="E13" s="12">
+        <f>'콜라비'!K4</f>
+        <v/>
+      </c>
+      <c r="F13" s="13">
+        <f>'콜라비'!L4</f>
+        <v/>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>⚠️마진 4%대 → 미끼 전용</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>📌 다음 액션:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1) 공급사에 '대극천복숭아 3kg' 매입가 요청 → 경쟁사 그램당 최저(3kg 693원/100g) 맞불용</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2) 보우짱 4kg·8kg 쿠팡 시세 실측 후 노란칸 교체(현재 보간 추정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3) 홍감자 시세는 쿠팡/오아시스 참고 추정 → 실제 검색가로 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4) 광고는 참외·복숭아·보우짱10kg에 집중, 콜라비3kg는 미끼로만</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A19:G19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -756,92 +1220,92 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>🟩공급가 실측(사진,롯데택배·박스포장 완충제 포함). 시세=쿠팡 시장조사. 실중량 2kg→1.5/3kg→2.5/5kg→4.5/10kg→9kg.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>등급</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>실중량</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>공급가(택배·포장포함)</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>건당광고비</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>당근수수료(3.3%)</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>총비용</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>시중시세(쿠팡)</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>손익분기가</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>당근권장가</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>마진(원)</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>마진율</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr"/>
-      <c r="D4" s="12" t="n">
+      <c r="C4" s="10" t="inlineStr"/>
+      <c r="D4" s="16" t="n">
         <v>4800</v>
       </c>
       <c r="E4" s="6">
@@ -852,26 +1316,26 @@
         <f>J4*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="17">
         <f>D4+E4+F4</f>
         <v/>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="H4" s="18" t="n">
         <v>12900</v>
       </c>
       <c r="I4" s="6">
         <f>ROUND((D4+E4)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="19">
         <f>ROUND(MAX(H4,(D4+E4)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="12">
         <f>J4-G4</f>
         <v/>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="13">
         <f>IF(J4=0,0,K4/J4)</f>
         <v/>
       </c>
@@ -881,22 +1345,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>1.5kg</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="16" t="n">
         <v>5900</v>
       </c>
       <c r="E5" s="6">
@@ -907,26 +1371,26 @@
         <f>J5*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="17">
         <f>D5+E5+F5</f>
         <v/>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="18" t="n">
         <v>21900</v>
       </c>
       <c r="I5" s="6">
         <f>ROUND((D5+E5)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="19">
         <f>ROUND(MAX(H5,(D5+E5)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="12">
         <f>J5-G5</f>
         <v/>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="13">
         <f>IF(J5=0,0,K5/J5)</f>
         <v/>
       </c>
@@ -936,22 +1400,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>2.5kg</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="16" t="n">
         <v>7350</v>
       </c>
       <c r="E6" s="6">
@@ -962,26 +1426,26 @@
         <f>J6*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="17">
         <f>D6+E6+F6</f>
         <v/>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="18" t="n">
         <v>26900</v>
       </c>
       <c r="I6" s="6">
         <f>ROUND((D6+E6)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="19">
         <f>ROUND(MAX(H6,(D6+E6)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="12">
         <f>J6-G6</f>
         <v/>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="13">
         <f>IF(J6=0,0,K6/J6)</f>
         <v/>
       </c>
@@ -991,22 +1455,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>4.5kg</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="16" t="n">
         <v>10500</v>
       </c>
       <c r="E7" s="6">
@@ -1017,26 +1481,26 @@
         <f>J7*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="17">
         <f>D7+E7+F7</f>
         <v/>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="18" t="n">
         <v>38800</v>
       </c>
       <c r="I7" s="6">
         <f>ROUND((D7+E7)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="19">
         <f>ROUND(MAX(H7,(D7+E7)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="12">
         <f>J7-G7</f>
         <v/>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="13">
         <f>IF(J7=0,0,K7/J7)</f>
         <v/>
       </c>
@@ -1046,22 +1510,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>9kg</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="16" t="n">
         <v>16900</v>
       </c>
       <c r="E8" s="6">
@@ -1072,26 +1536,26 @@
         <f>J8*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="17">
         <f>D8+E8+F8</f>
         <v/>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="18" t="n">
         <v>59000</v>
       </c>
       <c r="I8" s="6">
         <f>ROUND((D8+E8)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="19">
         <f>ROUND(MAX(H8,(D8+E8)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="12">
         <f>J8-G8</f>
         <v/>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="13">
         <f>IF(J8=0,0,K8/J8)</f>
         <v/>
       </c>
@@ -1101,18 +1565,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>소과</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr"/>
-      <c r="D9" s="12" t="n">
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="16" t="n">
         <v>4600</v>
       </c>
       <c r="E9" s="6">
@@ -1123,26 +1587,26 @@
         <f>J9*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="17">
         <f>D9+E9+F9</f>
         <v/>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="18" t="n">
         <v>10900</v>
       </c>
       <c r="I9" s="6">
         <f>ROUND((D9+E9)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="19">
         <f>ROUND(MAX(H9,(D9+E9)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="12">
         <f>J9-G9</f>
         <v/>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="13">
         <f>IF(J9=0,0,K9/J9)</f>
         <v/>
       </c>
@@ -1152,22 +1616,22 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>소과</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>1.5kg</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="16" t="n">
         <v>5600</v>
       </c>
       <c r="E10" s="6">
@@ -1178,26 +1642,26 @@
         <f>J10*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="17">
         <f>D10+E10+F10</f>
         <v/>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="18" t="n">
         <v>18900</v>
       </c>
       <c r="I10" s="6">
         <f>ROUND((D10+E10)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="19">
         <f>ROUND(MAX(H10,(D10+E10)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="12">
         <f>J10-G10</f>
         <v/>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="13">
         <f>IF(J10=0,0,K10/J10)</f>
         <v/>
       </c>
@@ -1207,22 +1671,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>소과</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>2.5kg</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="16" t="n">
         <v>6850</v>
       </c>
       <c r="E11" s="6">
@@ -1233,26 +1697,26 @@
         <f>J11*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="17">
         <f>D11+E11+F11</f>
         <v/>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="18" t="n">
         <v>19800</v>
       </c>
       <c r="I11" s="6">
         <f>ROUND((D11+E11)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="19">
         <f>ROUND(MAX(H11,(D11+E11)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="12">
         <f>J11-G11</f>
         <v/>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="13">
         <f>IF(J11=0,0,K11/J11)</f>
         <v/>
       </c>
@@ -1262,22 +1726,22 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>소과</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>4.5kg</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="16" t="n">
         <v>9600</v>
       </c>
       <c r="E12" s="6">
@@ -1288,26 +1752,26 @@
         <f>J12*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="17">
         <f>D12+E12+F12</f>
         <v/>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="18" t="n">
         <v>32000</v>
       </c>
       <c r="I12" s="6">
         <f>ROUND((D12+E12)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="19">
         <f>ROUND(MAX(H12,(D12+E12)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="12">
         <f>J12-G12</f>
         <v/>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="13">
         <f>IF(J12=0,0,K12/J12)</f>
         <v/>
       </c>
@@ -1317,22 +1781,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>소과</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>9kg</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="16" t="n">
         <v>15900</v>
       </c>
       <c r="E13" s="6">
@@ -1343,26 +1807,26 @@
         <f>J13*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="17">
         <f>D13+E13+F13</f>
         <v/>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="18" t="n">
         <v>53000</v>
       </c>
       <c r="I13" s="6">
         <f>ROUND((D13+E13)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="19">
         <f>ROUND(MAX(H13,(D13+E13)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="12">
         <f>J13-G13</f>
         <v/>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="13">
         <f>IF(J13=0,0,K13/J13)</f>
         <v/>
       </c>
@@ -1372,18 +1836,18 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>가성비혼합</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr"/>
-      <c r="D14" s="12" t="n">
+      <c r="C14" s="10" t="inlineStr"/>
+      <c r="D14" s="16" t="n">
         <v>4500</v>
       </c>
       <c r="E14" s="6">
@@ -1394,26 +1858,26 @@
         <f>J14*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="17">
         <f>D14+E14+F14</f>
         <v/>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="18" t="n">
         <v>9900</v>
       </c>
       <c r="I14" s="6">
         <f>ROUND((D14+E14)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="19">
         <f>ROUND(MAX(H14,(D14+E14)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="12">
         <f>J14-G14</f>
         <v/>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="13">
         <f>IF(J14=0,0,K14/J14)</f>
         <v/>
       </c>
@@ -1423,22 +1887,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>가성비혼합</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>1.5kg</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="16" t="n">
         <v>5300</v>
       </c>
       <c r="E15" s="6">
@@ -1449,26 +1913,26 @@
         <f>J15*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="17">
         <f>D15+E15+F15</f>
         <v/>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="18" t="n">
         <v>17900</v>
       </c>
       <c r="I15" s="6">
         <f>ROUND((D15+E15)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="19">
         <f>ROUND(MAX(H15,(D15+E15)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="12">
         <f>J15-G15</f>
         <v/>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="13">
         <f>IF(J15=0,0,K15/J15)</f>
         <v/>
       </c>
@@ -1478,22 +1942,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>가성비혼합</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>2.5kg</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="16" t="n">
         <v>6700</v>
       </c>
       <c r="E16" s="6">
@@ -1504,26 +1968,26 @@
         <f>J16*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="17">
         <f>D16+E16+F16</f>
         <v/>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H16" s="18" t="n">
         <v>16900</v>
       </c>
       <c r="I16" s="6">
         <f>ROUND((D16+E16)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="19">
         <f>ROUND(MAX(H16,(D16+E16)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="12">
         <f>J16-G16</f>
         <v/>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="13">
         <f>IF(J16=0,0,K16/J16)</f>
         <v/>
       </c>
@@ -1533,22 +1997,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>가성비혼합</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>4.5kg</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="16" t="n">
         <v>8500</v>
       </c>
       <c r="E17" s="6">
@@ -1559,26 +2023,26 @@
         <f>J17*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="17">
         <f>D17+E17+F17</f>
         <v/>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="H17" s="18" t="n">
         <v>29900</v>
       </c>
       <c r="I17" s="6">
         <f>ROUND((D17+E17)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="19">
         <f>ROUND(MAX(H17,(D17+E17)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="12">
         <f>J17-G17</f>
         <v/>
       </c>
-      <c r="L17" s="17">
+      <c r="L17" s="13">
         <f>IF(J17=0,0,K17/J17)</f>
         <v/>
       </c>
@@ -1588,22 +2052,22 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>가성비혼합</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>9kg</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="16" t="n">
         <v>11500</v>
       </c>
       <c r="E18" s="6">
@@ -1614,26 +2078,26 @@
         <f>J18*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="17">
         <f>D18+E18+F18</f>
         <v/>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="H18" s="18" t="n">
         <v>49900</v>
       </c>
       <c r="I18" s="6">
         <f>ROUND((D18+E18)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="19">
         <f>ROUND(MAX(H18,(D18+E18)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="12">
         <f>J18-G18</f>
         <v/>
       </c>
-      <c r="L18" s="17">
+      <c r="L18" s="13">
         <f>IF(J18=0,0,K18/J18)</f>
         <v/>
       </c>
@@ -1656,7 +2120,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1688,96 +2152,96 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>🟩공급가 실측(영천·김천 등 국내산,롯데택배,일반박스+쉘 벌크포장 포함,5~7월중순). 시세=쿠팡(로얄대과 1kg18,800·2kg28,800). 소과=11~16과/kg, 로얄과=4~10과/kg.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>등급</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>실중량</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>공급가(택배·포장포함)</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>건당광고비</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>당근수수료(3.3%)</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>총비용</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>시중시세(쿠팡)</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>손익분기가</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>당근권장가</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>마진(원)</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>마진율</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>4~10과</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="16" t="n">
         <v>9300</v>
       </c>
       <c r="E4" s="6">
@@ -1788,26 +2252,26 @@
         <f>J4*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="17">
         <f>D4+E4+F4</f>
         <v/>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="H4" s="18" t="n">
         <v>18800</v>
       </c>
       <c r="I4" s="6">
         <f>ROUND((D4+E4)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="19">
         <f>ROUND(MAX(H4,(D4+E4)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="12">
         <f>J4-G4</f>
         <v/>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="13">
         <f>IF(J4=0,0,K4/J4)</f>
         <v/>
       </c>
@@ -1817,22 +2281,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>8~20과</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="16" t="n">
         <v>15000</v>
       </c>
       <c r="E5" s="6">
@@ -1843,26 +2307,26 @@
         <f>J5*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="17">
         <f>D5+E5+F5</f>
         <v/>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="18" t="n">
         <v>28800</v>
       </c>
       <c r="I5" s="6">
         <f>ROUND((D5+E5)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="19">
         <f>ROUND(MAX(H5,(D5+E5)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="12">
         <f>J5-G5</f>
         <v/>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="13">
         <f>IF(J5=0,0,K5/J5)</f>
         <v/>
       </c>
@@ -1872,22 +2336,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>소과</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>11~16과</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="16" t="n">
         <v>6900</v>
       </c>
       <c r="E6" s="6">
@@ -1898,26 +2362,26 @@
         <f>J6*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="17">
         <f>D6+E6+F6</f>
         <v/>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="18" t="n">
         <v>14800</v>
       </c>
       <c r="I6" s="6">
         <f>ROUND((D6+E6)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="19">
         <f>ROUND(MAX(H6,(D6+E6)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="12">
         <f>J6-G6</f>
         <v/>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="13">
         <f>IF(J6=0,0,K6/J6)</f>
         <v/>
       </c>
@@ -1927,22 +2391,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>소과</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>21~32과</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="16" t="n">
         <v>11000</v>
       </c>
       <c r="E7" s="6">
@@ -1953,26 +2417,26 @@
         <f>J7*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="17">
         <f>D7+E7+F7</f>
         <v/>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="18" t="n">
         <v>22800</v>
       </c>
       <c r="I7" s="6">
         <f>ROUND((D7+E7)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="19">
         <f>ROUND(MAX(H7,(D7+E7)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="12">
         <f>J7-G7</f>
         <v/>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="13">
         <f>IF(J7=0,0,K7/J7)</f>
         <v/>
       </c>
@@ -1995,7 +2459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2027,96 +2491,96 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>🟩공급가 실측(제주,한진택배,무료배송 포함,비과세). 시세=쿠팡 판매가. ⚠️공급가가 시세에 매우 근접 → 저마진/손해 구간 많음.</t>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>🟩공급가 실측(제주,한진택배,무료배송 포함,비과세). 🟦시세=본인 쿠팡 리스팅 쿠폰가(=실판매가). 4kg·8kg 시세는 보간 추정(🟡노랑,조정).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>등급</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>실중량</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>공급가(택배·포장포함)</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>건당광고비</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>당근수수료(3.3%)</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>총비용</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>시중시세(쿠팡)</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>손익분기가</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>당근권장가</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>마진(원)</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>마진율</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>0.8kg</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="16" t="n">
         <v>5600</v>
       </c>
       <c r="E4" s="6">
@@ -2127,26 +2591,26 @@
         <f>J4*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="17">
         <f>D4+E4+F4</f>
         <v/>
       </c>
-      <c r="H4" s="14" t="n">
-        <v>5900</v>
+      <c r="H4" s="18" t="n">
+        <v>10800</v>
       </c>
       <c r="I4" s="6">
         <f>ROUND((D4+E4)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="19">
         <f>ROUND(MAX(H4,(D4+E4)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="12">
         <f>J4-G4</f>
         <v/>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="13">
         <f>IF(J4=0,0,K4/J4)</f>
         <v/>
       </c>
@@ -2156,22 +2620,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>1.5kg</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="16" t="n">
         <v>6900</v>
       </c>
       <c r="E5" s="6">
@@ -2182,26 +2646,26 @@
         <f>J5*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="17">
         <f>D5+E5+F5</f>
         <v/>
       </c>
-      <c r="H5" s="14" t="n">
-        <v>7700</v>
+      <c r="H5" s="18" t="n">
+        <v>14800</v>
       </c>
       <c r="I5" s="6">
         <f>ROUND((D5+E5)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="19">
         <f>ROUND(MAX(H5,(D5+E5)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="12">
         <f>J5-G5</f>
         <v/>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="13">
         <f>IF(J5=0,0,K5/J5)</f>
         <v/>
       </c>
@@ -2211,22 +2675,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>2.5kg</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="16" t="n">
         <v>8800</v>
       </c>
       <c r="E6" s="6">
@@ -2237,26 +2701,26 @@
         <f>J6*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="17">
         <f>D6+E6+F6</f>
         <v/>
       </c>
-      <c r="H6" s="14" t="n">
-        <v>9800</v>
+      <c r="H6" s="18" t="n">
+        <v>15800</v>
       </c>
       <c r="I6" s="6">
         <f>ROUND((D6+E6)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="19">
         <f>ROUND(MAX(H6,(D6+E6)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="12">
         <f>J6-G6</f>
         <v/>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="13">
         <f>IF(J6=0,0,K6/J6)</f>
         <v/>
       </c>
@@ -2266,22 +2730,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>4kg</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>3.5kg</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="16" t="n">
         <v>11200</v>
       </c>
       <c r="E7" s="6">
@@ -2292,26 +2756,26 @@
         <f>J7*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="17">
         <f>D7+E7+F7</f>
         <v/>
       </c>
-      <c r="H7" s="14" t="n">
-        <v>12400</v>
+      <c r="H7" s="3" t="n">
+        <v>17500</v>
       </c>
       <c r="I7" s="6">
         <f>ROUND((D7+E7)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="19">
         <f>ROUND(MAX(H7,(D7+E7)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="12">
         <f>J7-G7</f>
         <v/>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="13">
         <f>IF(J7=0,0,K7/J7)</f>
         <v/>
       </c>
@@ -2321,22 +2785,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>4.5kg</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="16" t="n">
         <v>12750</v>
       </c>
       <c r="E8" s="6">
@@ -2347,26 +2811,26 @@
         <f>J8*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="17">
         <f>D8+E8+F8</f>
         <v/>
       </c>
-      <c r="H8" s="14" t="n">
-        <v>14500</v>
+      <c r="H8" s="18" t="n">
+        <v>19800</v>
       </c>
       <c r="I8" s="6">
         <f>ROUND((D8+E8)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="19">
         <f>ROUND(MAX(H8,(D8+E8)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="12">
         <f>J8-G8</f>
         <v/>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="13">
         <f>IF(J8=0,0,K8/J8)</f>
         <v/>
       </c>
@@ -2376,22 +2840,22 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>8kg</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>7.5kg</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="16" t="n">
         <v>18600</v>
       </c>
       <c r="E9" s="6">
@@ -2402,26 +2866,26 @@
         <f>J9*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="17">
         <f>D9+E9+F9</f>
         <v/>
       </c>
-      <c r="H9" s="14" t="n">
-        <v>18900</v>
+      <c r="H9" s="3" t="n">
+        <v>31000</v>
       </c>
       <c r="I9" s="6">
         <f>ROUND((D9+E9)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="19">
         <f>ROUND(MAX(H9,(D9+E9)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="12">
         <f>J9-G9</f>
         <v/>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="13">
         <f>IF(J9=0,0,K9/J9)</f>
         <v/>
       </c>
@@ -2431,22 +2895,22 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>로얄과</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>9kg</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="16" t="n">
         <v>21300</v>
       </c>
       <c r="E10" s="6">
@@ -2457,26 +2921,26 @@
         <f>J10*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="17">
         <f>D10+E10+F10</f>
         <v/>
       </c>
-      <c r="H10" s="14" t="n">
-        <v>24400</v>
+      <c r="H10" s="18" t="n">
+        <v>38800</v>
       </c>
       <c r="I10" s="6">
         <f>ROUND((D10+E10)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="19">
         <f>ROUND(MAX(H10,(D10+E10)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="12">
         <f>J10-G10</f>
         <v/>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="13">
         <f>IF(J10=0,0,K10/J10)</f>
         <v/>
       </c>
@@ -2499,7 +2963,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2531,92 +2995,92 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>🟩공급가 실측(남해 등 국내산,롯데택배,농산물박스 포함). 🟦시세=쿠팡/오아시스마켓 참고(대 3kg13,900·5kg19,900)-조정가능.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>등급</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>실중량</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>공급가(택배·포장포함)</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>건당광고비</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>당근수수료(3.3%)</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>총비용</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>시중시세(쿠팡)</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>손익분기가</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>당근권장가</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>마진(원)</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>마진율</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>소</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr"/>
-      <c r="D4" s="12" t="n">
+      <c r="C4" s="10" t="inlineStr"/>
+      <c r="D4" s="16" t="n">
         <v>4200</v>
       </c>
       <c r="E4" s="6">
@@ -2627,26 +3091,26 @@
         <f>J4*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="17">
         <f>D4+E4+F4</f>
         <v/>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="H4" s="18" t="n">
         <v>4900</v>
       </c>
       <c r="I4" s="6">
         <f>ROUND((D4+E4)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="19">
         <f>ROUND(MAX(H4,(D4+E4)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="12">
         <f>J4-G4</f>
         <v/>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="13">
         <f>IF(J4=0,0,K4/J4)</f>
         <v/>
       </c>
@@ -2656,18 +3120,18 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>소</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr"/>
-      <c r="D5" s="12" t="n">
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="16" t="n">
         <v>5500</v>
       </c>
       <c r="E5" s="6">
@@ -2678,26 +3142,26 @@
         <f>J5*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="17">
         <f>D5+E5+F5</f>
         <v/>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="18" t="n">
         <v>7500</v>
       </c>
       <c r="I5" s="6">
         <f>ROUND((D5+E5)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="19">
         <f>ROUND(MAX(H5,(D5+E5)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="12">
         <f>J5-G5</f>
         <v/>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="13">
         <f>IF(J5=0,0,K5/J5)</f>
         <v/>
       </c>
@@ -2707,18 +3171,18 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>소</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr"/>
-      <c r="D6" s="12" t="n">
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="16" t="n">
         <v>6600</v>
       </c>
       <c r="E6" s="6">
@@ -2729,26 +3193,26 @@
         <f>J6*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="17">
         <f>D6+E6+F6</f>
         <v/>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="18" t="n">
         <v>9900</v>
       </c>
       <c r="I6" s="6">
         <f>ROUND((D6+E6)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="19">
         <f>ROUND(MAX(H6,(D6+E6)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="12">
         <f>J6-G6</f>
         <v/>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="13">
         <f>IF(J6=0,0,K6/J6)</f>
         <v/>
       </c>
@@ -2758,18 +3222,18 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>소</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr"/>
-      <c r="D7" s="12" t="n">
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="16" t="n">
         <v>9500</v>
       </c>
       <c r="E7" s="6">
@@ -2780,26 +3244,26 @@
         <f>J7*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="17">
         <f>D7+E7+F7</f>
         <v/>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="18" t="n">
         <v>13900</v>
       </c>
       <c r="I7" s="6">
         <f>ROUND((D7+E7)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="19">
         <f>ROUND(MAX(H7,(D7+E7)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="12">
         <f>J7-G7</f>
         <v/>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="13">
         <f>IF(J7=0,0,K7/J7)</f>
         <v/>
       </c>
@@ -2809,18 +3273,18 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr"/>
-      <c r="D8" s="12" t="n">
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="16" t="n">
         <v>4300</v>
       </c>
       <c r="E8" s="6">
@@ -2831,26 +3295,26 @@
         <f>J8*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="17">
         <f>D8+E8+F8</f>
         <v/>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="18" t="n">
         <v>5500</v>
       </c>
       <c r="I8" s="6">
         <f>ROUND((D8+E8)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="19">
         <f>ROUND(MAX(H8,(D8+E8)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="12">
         <f>J8-G8</f>
         <v/>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="13">
         <f>IF(J8=0,0,K8/J8)</f>
         <v/>
       </c>
@@ -2860,18 +3324,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr"/>
-      <c r="D9" s="12" t="n">
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="16" t="n">
         <v>5700</v>
       </c>
       <c r="E9" s="6">
@@ -2882,26 +3346,26 @@
         <f>J9*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="17">
         <f>D9+E9+F9</f>
         <v/>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="18" t="n">
         <v>8500</v>
       </c>
       <c r="I9" s="6">
         <f>ROUND((D9+E9)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="19">
         <f>ROUND(MAX(H9,(D9+E9)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="12">
         <f>J9-G9</f>
         <v/>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="13">
         <f>IF(J9=0,0,K9/J9)</f>
         <v/>
       </c>
@@ -2911,18 +3375,18 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr"/>
-      <c r="D10" s="12" t="n">
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="16" t="n">
         <v>6900</v>
       </c>
       <c r="E10" s="6">
@@ -2933,26 +3397,26 @@
         <f>J10*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="17">
         <f>D10+E10+F10</f>
         <v/>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="18" t="n">
         <v>11900</v>
       </c>
       <c r="I10" s="6">
         <f>ROUND((D10+E10)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="19">
         <f>ROUND(MAX(H10,(D10+E10)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="12">
         <f>J10-G10</f>
         <v/>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="13">
         <f>IF(J10=0,0,K10/J10)</f>
         <v/>
       </c>
@@ -2962,18 +3426,18 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr"/>
-      <c r="D11" s="12" t="n">
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="16" t="n">
         <v>10000</v>
       </c>
       <c r="E11" s="6">
@@ -2984,26 +3448,26 @@
         <f>J11*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="17">
         <f>D11+E11+F11</f>
         <v/>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="18" t="n">
         <v>16900</v>
       </c>
       <c r="I11" s="6">
         <f>ROUND((D11+E11)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="19">
         <f>ROUND(MAX(H11,(D11+E11)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="12">
         <f>J11-G11</f>
         <v/>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="13">
         <f>IF(J11=0,0,K11/J11)</f>
         <v/>
       </c>
@@ -3013,18 +3477,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>대</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr"/>
-      <c r="D12" s="12" t="n">
+      <c r="C12" s="10" t="inlineStr"/>
+      <c r="D12" s="16" t="n">
         <v>5300</v>
       </c>
       <c r="E12" s="6">
@@ -3035,26 +3499,26 @@
         <f>J12*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="17">
         <f>D12+E12+F12</f>
         <v/>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="18" t="n">
         <v>6900</v>
       </c>
       <c r="I12" s="6">
         <f>ROUND((D12+E12)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="19">
         <f>ROUND(MAX(H12,(D12+E12)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="12">
         <f>J12-G12</f>
         <v/>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="13">
         <f>IF(J12=0,0,K12/J12)</f>
         <v/>
       </c>
@@ -3064,18 +3528,18 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>대</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr"/>
-      <c r="D13" s="12" t="n">
+      <c r="C13" s="10" t="inlineStr"/>
+      <c r="D13" s="16" t="n">
         <v>6900</v>
       </c>
       <c r="E13" s="6">
@@ -3086,26 +3550,26 @@
         <f>J13*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="17">
         <f>D13+E13+F13</f>
         <v/>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="18" t="n">
         <v>9900</v>
       </c>
       <c r="I13" s="6">
         <f>ROUND((D13+E13)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="19">
         <f>ROUND(MAX(H13,(D13+E13)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="12">
         <f>J13-G13</f>
         <v/>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="13">
         <f>IF(J13=0,0,K13/J13)</f>
         <v/>
       </c>
@@ -3115,18 +3579,18 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>대</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr"/>
-      <c r="D14" s="12" t="n">
+      <c r="C14" s="10" t="inlineStr"/>
+      <c r="D14" s="16" t="n">
         <v>8400</v>
       </c>
       <c r="E14" s="6">
@@ -3137,26 +3601,26 @@
         <f>J14*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="17">
         <f>D14+E14+F14</f>
         <v/>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="18" t="n">
         <v>13900</v>
       </c>
       <c r="I14" s="6">
         <f>ROUND((D14+E14)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="19">
         <f>ROUND(MAX(H14,(D14+E14)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="12">
         <f>J14-G14</f>
         <v/>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="13">
         <f>IF(J14=0,0,K14/J14)</f>
         <v/>
       </c>
@@ -3166,18 +3630,18 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>대</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="12" t="n">
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="16" t="n">
         <v>12500</v>
       </c>
       <c r="E15" s="6">
@@ -3188,26 +3652,26 @@
         <f>J15*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="17">
         <f>D15+E15+F15</f>
         <v/>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="18" t="n">
         <v>19900</v>
       </c>
       <c r="I15" s="6">
         <f>ROUND((D15+E15)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="19">
         <f>ROUND(MAX(H15,(D15+E15)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="12">
         <f>J15-G15</f>
         <v/>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="13">
         <f>IF(J15=0,0,K15/J15)</f>
         <v/>
       </c>
@@ -3217,18 +3681,18 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>특</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr"/>
-      <c r="D16" s="12" t="n">
+      <c r="C16" s="10" t="inlineStr"/>
+      <c r="D16" s="16" t="n">
         <v>6000</v>
       </c>
       <c r="E16" s="6">
@@ -3239,26 +3703,26 @@
         <f>J16*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="17">
         <f>D16+E16+F16</f>
         <v/>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H16" s="18" t="n">
         <v>7500</v>
       </c>
       <c r="I16" s="6">
         <f>ROUND((D16+E16)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="19">
         <f>ROUND(MAX(H16,(D16+E16)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="12">
         <f>J16-G16</f>
         <v/>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="13">
         <f>IF(J16=0,0,K16/J16)</f>
         <v/>
       </c>
@@ -3268,18 +3732,18 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>특</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr"/>
-      <c r="D17" s="12" t="n">
+      <c r="C17" s="10" t="inlineStr"/>
+      <c r="D17" s="16" t="n">
         <v>8300</v>
       </c>
       <c r="E17" s="6">
@@ -3290,26 +3754,26 @@
         <f>J17*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="17">
         <f>D17+E17+F17</f>
         <v/>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="H17" s="18" t="n">
         <v>10900</v>
       </c>
       <c r="I17" s="6">
         <f>ROUND((D17+E17)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="19">
         <f>ROUND(MAX(H17,(D17+E17)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="12">
         <f>J17-G17</f>
         <v/>
       </c>
-      <c r="L17" s="17">
+      <c r="L17" s="13">
         <f>IF(J17=0,0,K17/J17)</f>
         <v/>
       </c>
@@ -3319,18 +3783,18 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>특</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr"/>
-      <c r="D18" s="12" t="n">
+      <c r="C18" s="10" t="inlineStr"/>
+      <c r="D18" s="16" t="n">
         <v>10500</v>
       </c>
       <c r="E18" s="6">
@@ -3341,26 +3805,26 @@
         <f>J18*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="17">
         <f>D18+E18+F18</f>
         <v/>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="H18" s="18" t="n">
         <v>14900</v>
       </c>
       <c r="I18" s="6">
         <f>ROUND((D18+E18)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="19">
         <f>ROUND(MAX(H18,(D18+E18)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="12">
         <f>J18-G18</f>
         <v/>
       </c>
-      <c r="L18" s="17">
+      <c r="L18" s="13">
         <f>IF(J18=0,0,K18/J18)</f>
         <v/>
       </c>
@@ -3370,18 +3834,18 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>특</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr"/>
-      <c r="D19" s="12" t="n">
+      <c r="C19" s="10" t="inlineStr"/>
+      <c r="D19" s="16" t="n">
         <v>15500</v>
       </c>
       <c r="E19" s="6">
@@ -3392,26 +3856,26 @@
         <f>J19*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="17">
         <f>D19+E19+F19</f>
         <v/>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="H19" s="18" t="n">
         <v>22900</v>
       </c>
       <c r="I19" s="6">
         <f>ROUND((D19+E19)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="19">
         <f>ROUND(MAX(H19,(D19+E19)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="12">
         <f>J19-G19</f>
         <v/>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="13">
         <f>IF(J19=0,0,K19/J19)</f>
         <v/>
       </c>
@@ -3421,18 +3885,18 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>왕특</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr"/>
-      <c r="D20" s="12" t="n">
+      <c r="C20" s="10" t="inlineStr"/>
+      <c r="D20" s="16" t="n">
         <v>6300</v>
       </c>
       <c r="E20" s="6">
@@ -3443,26 +3907,26 @@
         <f>J20*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="17">
         <f>D20+E20+F20</f>
         <v/>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="18" t="n">
         <v>7900</v>
       </c>
       <c r="I20" s="6">
         <f>ROUND((D20+E20)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="19">
         <f>ROUND(MAX(H20,(D20+E20)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="12">
         <f>J20-G20</f>
         <v/>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="13">
         <f>IF(J20=0,0,K20/J20)</f>
         <v/>
       </c>
@@ -3472,18 +3936,18 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>왕특</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>2kg</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr"/>
-      <c r="D21" s="12" t="n">
+      <c r="C21" s="10" t="inlineStr"/>
+      <c r="D21" s="16" t="n">
         <v>8800</v>
       </c>
       <c r="E21" s="6">
@@ -3494,26 +3958,26 @@
         <f>J21*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="17">
         <f>D21+E21+F21</f>
         <v/>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="H21" s="18" t="n">
         <v>11900</v>
       </c>
       <c r="I21" s="6">
         <f>ROUND((D21+E21)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="19">
         <f>ROUND(MAX(H21,(D21+E21)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="12">
         <f>J21-G21</f>
         <v/>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="13">
         <f>IF(J21=0,0,K21/J21)</f>
         <v/>
       </c>
@@ -3523,18 +3987,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>왕특</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr"/>
-      <c r="D22" s="12" t="n">
+      <c r="C22" s="10" t="inlineStr"/>
+      <c r="D22" s="16" t="n">
         <v>11700</v>
       </c>
       <c r="E22" s="6">
@@ -3545,26 +4009,26 @@
         <f>J22*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="17">
         <f>D22+E22+F22</f>
         <v/>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="H22" s="18" t="n">
         <v>16900</v>
       </c>
       <c r="I22" s="6">
         <f>ROUND((D22+E22)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="19">
         <f>ROUND(MAX(H22,(D22+E22)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="12">
         <f>J22-G22</f>
         <v/>
       </c>
-      <c r="L22" s="17">
+      <c r="L22" s="13">
         <f>IF(J22=0,0,K22/J22)</f>
         <v/>
       </c>
@@ -3574,18 +4038,18 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>왕특</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr"/>
-      <c r="D23" s="12" t="n">
+      <c r="C23" s="10" t="inlineStr"/>
+      <c r="D23" s="16" t="n">
         <v>18000</v>
       </c>
       <c r="E23" s="6">
@@ -3596,26 +4060,26 @@
         <f>J23*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="17">
         <f>D23+E23+F23</f>
         <v/>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="H23" s="18" t="n">
         <v>24800</v>
       </c>
       <c r="I23" s="6">
         <f>ROUND((D23+E23)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="19">
         <f>ROUND(MAX(H23,(D23+E23)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="12">
         <f>J23-G23</f>
         <v/>
       </c>
-      <c r="L23" s="17">
+      <c r="L23" s="13">
         <f>IF(J23=0,0,K23/J23)</f>
         <v/>
       </c>
@@ -3638,7 +4102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3670,92 +4134,92 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>🟩공급가 확정(소싱현황). 시세=쿠팡 최종쿠폰가.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>등급</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>옵션</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>실중량</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>공급가(택배·포장포함)</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>건당광고비</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>당근수수료(3.3%)</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>총비용</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>시중시세(쿠팡)</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>손익분기가</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>당근권장가</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>마진(원)</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>마진율</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>정품</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>3kg</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr"/>
-      <c r="D4" s="12" t="n">
+      <c r="C4" s="10" t="inlineStr"/>
+      <c r="D4" s="16" t="n">
         <v>9500</v>
       </c>
       <c r="E4" s="6">
@@ -3766,26 +4230,26 @@
         <f>J4*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="17">
         <f>D4+E4+F4</f>
         <v/>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="H4" s="18" t="n">
         <v>12420</v>
       </c>
       <c r="I4" s="6">
         <f>ROUND((D4+E4)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="19">
         <f>ROUND(MAX(H4,(D4+E4)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="12">
         <f>J4-G4</f>
         <v/>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="13">
         <f>IF(J4=0,0,K4/J4)</f>
         <v/>
       </c>
@@ -3795,18 +4259,18 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>정품</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr"/>
-      <c r="D5" s="12" t="n">
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="16" t="n">
         <v>13200</v>
       </c>
       <c r="E5" s="6">
@@ -3817,26 +4281,26 @@
         <f>J5*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="17">
         <f>D5+E5+F5</f>
         <v/>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="18" t="n">
         <v>19050</v>
       </c>
       <c r="I5" s="6">
         <f>ROUND((D5+E5)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="19">
         <f>ROUND(MAX(H5,(D5+E5)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="12">
         <f>J5-G5</f>
         <v/>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="13">
         <f>IF(J5=0,0,K5/J5)</f>
         <v/>
       </c>
@@ -3846,18 +4310,18 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>정품</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>10kg</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr"/>
-      <c r="D6" s="12" t="n">
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="16" t="n">
         <v>22700</v>
       </c>
       <c r="E6" s="6">
@@ -3868,26 +4332,26 @@
         <f>J6*'설정'!$B$6</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="17">
         <f>D6+E6+F6</f>
         <v/>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="18" t="n">
         <v>29390</v>
       </c>
       <c r="I6" s="6">
         <f>ROUND((D6+E6)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="19">
         <f>ROUND(MAX(H6,(D6+E6)/(1-'설정'!$B$6-'설정'!$B$7)),-2)</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="12">
         <f>J6-G6</f>
         <v/>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="13">
         <f>IF(J6=0,0,K6/J6)</f>
         <v/>
       </c>
@@ -3910,7 +4374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3940,364 +4404,364 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>대응권장가=경쟁사보다 300원↓(단 손익분기 이상). 마진/손익분기는 설정값(광고·수수료3.3%) 자동 연동. 그램당으로 보면 경쟁사 3kg가 진짜 무기.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>경쟁사 옵션</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>경쟁사가</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>경쟁사 100g당</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>우리 매칭</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>우리 공급가</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>우리 손익분기</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>대응 권장가</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>우리 마진</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>우리 마진율</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>우리 100g당</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>소과 2kg(60g/개)</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="12" t="n">
         <v>16100</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="12">
         <f>ROUND(B4/20.0,0)</f>
         <v/>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>우리 소과 2kg</t>
         </is>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="16" t="n">
         <v>11000</v>
       </c>
       <c r="F4" s="6">
         <f>ROUND((E4+'설정'!$B$5)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="19">
         <f>ROUND(MAX(F4,B4-300),-2)</f>
         <v/>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="12">
         <f>G4*(1-'설정'!$B$6)-E4-'설정'!$B$5</f>
         <v/>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="13">
         <f>IF(G4=0,0,H4/G4)</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="12">
         <f>ROUND(G4/20.0,0)</f>
         <v/>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="14">
         <f>IF(B4-300&gt;=F4,"✅ 이길 수 있음","⚠️ 빠듯")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>중과 2kg(80g/개)</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="12" t="n">
         <v>18200</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="12">
         <f>ROUND(B5/20.0,0)</f>
         <v/>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>우리 소과 2kg</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="16" t="n">
         <v>11000</v>
       </c>
       <c r="F5" s="6">
         <f>ROUND((E5+'설정'!$B$5)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="19">
         <f>ROUND(MAX(F5,B5-300),-2)</f>
         <v/>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="12">
         <f>G5*(1-'설정'!$B$6)-E5-'설정'!$B$5</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="13">
         <f>IF(G5=0,0,H5/G5)</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="12">
         <f>ROUND(G5/20.0,0)</f>
         <v/>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="14">
         <f>IF(B5-300&gt;=F5,"✅ 이길 수 있음","⚠️ 빠듯")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>대과 2kg(100g/개)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="12" t="n">
         <v>21000</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="12">
         <f>ROUND(B6/20.0,0)</f>
         <v/>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>우리 로얄과 2kg</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="16" t="n">
         <v>15000</v>
       </c>
       <c r="F6" s="6">
         <f>ROUND((E6+'설정'!$B$5)/(1-'설정'!$B$6),-2)</f>
         <v/>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="19">
         <f>ROUND(MAX(F6,B6-300),-2)</f>
         <v/>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="12">
         <f>G6*(1-'설정'!$B$6)-E6-'설정'!$B$5</f>
         <v/>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="13">
         <f>IF(G6=0,0,H6/G6)</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="12">
         <f>ROUND(G6/20.0,0)</f>
         <v/>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="14">
         <f>IF(B6-300&gt;=F6,"✅ 이길 수 있음","⚠️ 빠듯")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>소과 3kg(60g/개)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="12" t="n">
         <v>20800</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="12">
         <f>ROUND(B7/30.0,0)</f>
         <v/>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>우리 3kg 공급 없음</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t>❓3kg 매입가 협의 필요</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>중과 3kg(80g/개)</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="12" t="n">
         <v>21500</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="12">
         <f>ROUND(B8/30.0,0)</f>
         <v/>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>우리 3kg 공급 없음</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K8" s="19" t="inlineStr">
+      <c r="K8" s="14" t="inlineStr">
         <is>
           <t>❓3kg 매입가 협의 필요</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>대과 3kg(100g/개)</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="12" t="n">
         <v>25200</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="12">
         <f>ROUND(B9/30.0,0)</f>
         <v/>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>우리 3kg 공급 없음</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K9" s="19" t="inlineStr">
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t>❓3kg 매입가 협의 필요</t>
         </is>
